--- a/output/laminas_provinciales/prov_i_ingr_a_2023_arica_y_parinacota.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_a_2023_arica_y_parinacota.xlsx
@@ -353,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -417,7 +417,7 @@
         <v>2.272935821509936</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -444,7 +444,7 @@
         <v>17.5037127424535</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -471,13 +471,13 @@
         <v>11.41439218523019</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Arica</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -486,25 +486,25 @@
         </is>
       </c>
       <c r="C5">
-        <v>973498.6899999999</v>
+        <v>972085.5</v>
       </c>
       <c r="D5">
-        <v>854315</v>
+        <v>853445.25</v>
       </c>
       <c r="E5">
-        <v>119183.6899999999</v>
+        <v>118640.25</v>
       </c>
       <c r="F5">
-        <v>13.95078981406155</v>
+        <v>13.90133110471936</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Arica</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -513,45 +513,126 @@
         </is>
       </c>
       <c r="C6">
-        <v>1198550.5</v>
+        <v>1197122.25</v>
       </c>
       <c r="D6">
-        <v>1072154.12</v>
+        <v>1070632.25</v>
       </c>
       <c r="E6">
-        <v>126396.3799999999</v>
+        <v>126490</v>
       </c>
       <c r="F6">
-        <v>11.78901219910435</v>
+        <v>11.81451427415903</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Promedio Regional</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>1099959.12</v>
+      </c>
+      <c r="D7">
+        <v>977578.5600000001</v>
+      </c>
+      <c r="E7">
+        <v>122380.5600000001</v>
+      </c>
+      <c r="F7">
+        <v>12.518744273606</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>Arica</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>973498.6899999999</v>
+      </c>
+      <c r="D8">
+        <v>854315</v>
+      </c>
+      <c r="E8">
+        <v>119183.6899999999</v>
+      </c>
+      <c r="F8">
+        <v>13.95078981406155</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>1198550.5</v>
+      </c>
+      <c r="D9">
+        <v>1072154.12</v>
+      </c>
+      <c r="E9">
+        <v>126396.3799999999</v>
+      </c>
+      <c r="F9">
+        <v>11.78901219910435</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Arica</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C7">
+      <c r="C10">
         <v>1101375</v>
       </c>
-      <c r="D7">
+      <c r="D10">
         <v>978811.0600000001</v>
       </c>
-      <c r="E7">
+      <c r="E10">
         <v>122563.9399999999</v>
       </c>
-      <c r="F7">
+      <c r="F10">
         <v>12.52171588661861</v>
       </c>
-      <c r="G7">
+      <c r="G10">
         <v>1</v>
       </c>
     </row>
@@ -604,7 +685,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -737,6 +818,60 @@
         <v>0</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Promedio Regional</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>977578.5600000001</v>
+      </c>
+      <c r="D8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Promedio Regional</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>1099959.12</v>
+      </c>
+      <c r="D9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Promedio Regional</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>1185102.25</v>
+      </c>
+      <c r="D10" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/output/laminas_provinciales/prov_i_ingr_a_2023_arica_y_parinacota.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_a_2023_arica_y_parinacota.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t xml:space="preserve">Provincia</t>
   </si>
@@ -68,7 +68,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 22:04</t>
+    <t xml:space="preserve">2026-08-19 14:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -80,13 +80,19 @@
     <t xml:space="preserve">Imagen asociada</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t xml:space="preserve">prov_i_ingr_a_2023_arica_y_parinacota.png</t>
   </si>
   <si>
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
+    <t xml:space="preserve">Ingreso de asalariados formales</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unidad territorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Region de Arica y Parinacota</t>
   </si>
   <si>
     <t xml:space="preserve">Año</t>
@@ -761,23 +767,23 @@
         <v>21</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -800,7 +806,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2">
@@ -841,10 +847,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2">
@@ -852,7 +858,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>978811.06</v>
@@ -863,7 +869,7 @@
         <v>12</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>1101375</v>
@@ -874,7 +880,7 @@
         <v>12</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>1186511.5</v>
@@ -885,7 +891,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>750279.81</v>
@@ -896,7 +902,7 @@
         <v>7</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>835919.69</v>
@@ -907,7 +913,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>930762.5</v>
@@ -918,7 +924,7 @@
         <v>11</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>977578.56</v>
@@ -929,7 +935,7 @@
         <v>11</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>1099959.12</v>
@@ -940,7 +946,7 @@
         <v>11</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>1185102.25</v>

--- a/output/laminas_provinciales/prov_i_ingr_a_2023_arica_y_parinacota.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_a_2023_arica_y_parinacota.xlsx
@@ -68,7 +68,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 14:23</t>
+    <t xml:space="preserve">2026-09-07 11:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
